--- a/inst/extdata/test_file_1.xlsx
+++ b/inst/extdata/test_file_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalar\RstudioProjects\ProtStatsWF\examples\examples_ttest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schorkka\Documents\Projects\Statistik_Workflows\ProtStatsWF\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560B972F-C69F-4A5B-81B6-1A0ED2808C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B82947-58A6-4BF0-8B75-278F117B2C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3240" yWindow="-17220" windowWidth="16755" windowHeight="12345" xr2:uid="{0F594E3C-BF59-4F3E-939E-9ACCDDEA93B9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F594E3C-BF59-4F3E-939E-9ACCDDEA93B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1020,9 +1020,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A739B8B-732D-47DA-8D1E-D31100E7F0C1}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>34910128</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>33763808</v>
       </c>
       <c r="E2">
         <v>33763808</v>
@@ -1092,7 +1095,7 @@
         <v>39887340</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>228724928</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>230557560</v>
       </c>
       <c r="E3">
         <v>230557560</v>
@@ -1127,7 +1130,7 @@
         <v>287809476</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1138,7 +1141,7 @@
         <v>25142570</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>24140170</v>
       </c>
       <c r="E4">
         <v>24140170</v>
@@ -1162,7 +1165,7 @@
         <v>26086670</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>26402860</v>
       </c>
       <c r="E6">
         <v>26402860</v>
@@ -1232,7 +1235,7 @@
         <v>8003230</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>23729240</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>22417890</v>
       </c>
       <c r="E7">
         <v>22417890</v>
@@ -1267,7 +1270,7 @@
         <v>22170380</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1278,7 +1281,7 @@
         <v>36068288</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>38500928</v>
       </c>
       <c r="E8">
         <v>38500928</v>
@@ -1302,7 +1305,7 @@
         <v>36233440</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1313,7 +1316,7 @@
         <v>37990528</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>32654220</v>
       </c>
       <c r="E9">
         <v>32654220</v>
@@ -1337,7 +1340,7 @@
         <v>34394968</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1348,7 +1351,7 @@
         <v>2590670618</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2707158182</v>
       </c>
       <c r="E10">
         <v>2707158182</v>
@@ -1372,7 +1375,7 @@
         <v>2587524814</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>2531858</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>52227550</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>52181250</v>
       </c>
       <c r="E12">
         <v>52181250</v>
@@ -1442,7 +1445,7 @@
         <v>53973140</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>5683145</v>
       </c>
       <c r="E13">
         <v>5683145</v>
@@ -1477,7 +1480,7 @@
         <v>8344295</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>49514448</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>50004128</v>
       </c>
       <c r="E14">
         <v>50004128</v>
@@ -1512,7 +1515,7 @@
         <v>43506848</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1547,7 +1550,7 @@
         <v>13158910</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1558,7 +1561,7 @@
         <v>53367728</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>60332520</v>
       </c>
       <c r="E16">
         <v>60332520</v>
